--- a/ArbolesDecision/Dataset/heart_failure_clinical_records_dataset.xlsx
+++ b/ArbolesDecision/Dataset/heart_failure_clinical_records_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python2026\business-intelligence\ArbolesDecision\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB1E98-1690-47D9-BD9A-722DCD3E0131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79F961D-9EB6-40AB-9D17-A2430D4E6AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="10500" xr2:uid="{E42C2B9C-F5B2-4281-B725-3142C63FCC37}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E42C2B9C-F5B2-4281-B725-3142C63FCC37}"/>
   </bookViews>
   <sheets>
     <sheet name="heart_failure_clinical_records_" sheetId="2" r:id="rId1"/>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="190" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>60</v>
+        <v>60667</v>
       </c>
       <c r="B190" s="1">
         <v>1</v>
